--- a/results/Int All Data -0.2/Rando_10_permute.xlsx
+++ b/results/Int All Data -0.2/Rando_10_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8544902324646002</v>
+        <v>0.8562094300532774</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8551442547013561</v>
+        <v>0.8571998125191657</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8545089306861084</v>
+        <v>0.8576109656343309</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8538642575601065</v>
+        <v>0.8551631606808812</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8562000809425233</v>
+        <v>0.854826800451749</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8565177429501472</v>
+        <v>0.8584987156399404</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8574987763052813</v>
+        <v>0.8584987156399404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8575174745267895</v>
+        <v>0.8584987156399404</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8598252505769439</v>
+        <v>0.8455772057876397</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.860806283932078</v>
+        <v>0.8503423436600148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8621236775163443</v>
+        <v>0.8470909306977428</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8577883909806427</v>
+        <v>0.8455400171026399</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.864123140669629</v>
+        <v>0.843260288384748</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8702617667907951</v>
+        <v>0.8411953814561843</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8488097127703866</v>
+        <v>0.8424847277081881</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.848174388755139</v>
+        <v>0.844110434189324</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8472214027322672</v>
+        <v>0.8451101657659664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8468663442816269</v>
+        <v>0.8469693922579391</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8402326308065249</v>
+        <v>0.869532951668006</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.840896002154035</v>
+        <v>0.8714576219352577</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8426245488534666</v>
+        <v>0.8717939821643897</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.842904814418074</v>
+        <v>0.8689911187602997</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8448668811283421</v>
+        <v>0.8686734567526757</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8455022051435899</v>
+        <v>0.8735877648810835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.847539064739891</v>
+        <v>0.856219194680065</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8567234233867382</v>
+        <v>0.8572748131632155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8539297013353855</v>
+        <v>0.8585548103044651</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8539297013353855</v>
+        <v>0.8585548103044651</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8502764843687023</v>
+        <v>0.8553781902282263</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8502764843687023</v>
+        <v>0.8681033687546902</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8538923048923689</v>
+        <v>0.8718966146246685</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8535559446632367</v>
+        <v>0.8688508820989875</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8511548852635576</v>
+        <v>0.870439192137107</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8463525587061828</v>
+        <v>0.8644036139922531</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8489499494316988</v>
+        <v>0.8586669996335148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8505663068020806</v>
+        <v>0.8586669996335148</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8478382362840235</v>
+        <v>0.8607223496933076</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8457174424489518</v>
+        <v>0.8521922210412334</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8512859805721323</v>
+        <v>0.8602927061146508</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8233217515164257</v>
+        <v>0.8550139904248485</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8233217515164257</v>
+        <v>0.8546776301957164</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8270312709056504</v>
+        <v>0.8623295657109521</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8162866495529464</v>
+        <v>0.8528744983682686</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8162866495529464</v>
+        <v>0.8506882607579178</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8179217051448364</v>
+        <v>0.846212945318921</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8191551644903322</v>
+        <v>0.8455682721929191</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8137268630284638</v>
+        <v>0.8445030968409979</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8177725348888037</v>
+        <v>0.8457737448714934</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8332444821548329</v>
+        <v>0.8461568506543962</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8332444821548329</v>
+        <v>0.8474274986848918</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8164831886368</v>
+        <v>0.8478293026893029</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8253588188707437</v>
+        <v>0.8434661765793556</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8293951416203297</v>
+        <v>0.8462970873157083</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8293951416203297</v>
+        <v>0.8345061965906078</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.824331039961839</v>
+        <v>0.830161768702169</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8035149332307285</v>
+        <v>0.8323947518662903</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8031879221123506</v>
+        <v>0.8338989199076224</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8037578023523193</v>
+        <v>0.8418498192089738</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8057385672840958</v>
+        <v>0.8357768446211034</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7882110622002572</v>
+        <v>0.8323197512222404</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7862302972684807</v>
+        <v>0.8263963624064362</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7977502715397279</v>
+        <v>0.8134750603121523</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.80718684841892</v>
+        <v>0.8138114205412844</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7846050063033783</v>
+        <v>0.8030015631713181</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7771120056709628</v>
+        <v>0.7900054681910011</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7546795415694705</v>
+        <v>0.79843275662478</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7543431813403384</v>
+        <v>0.7987504186324038</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7537172064358448</v>
+        <v>0.7997314519875378</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7653119735931251</v>
+        <v>0.7863616003350722</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7247353786140546</v>
+        <v>0.7857169272090703</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7190268115875786</v>
+        <v>0.7847826394077069</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7101042280418475</v>
+        <v>0.7847826394077069</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6657719913938319</v>
+        <v>0.7835306895987195</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6881205212565538</v>
+        <v>0.779662650842708</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6600916794576352</v>
+        <v>0.7989652404217321</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.654682076217275</v>
+        <v>0.7878562115076335</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6552987020110145</v>
+        <v>0.7956857801271977</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5727722315620993</v>
+        <v>0.7950317578904418</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5721369075468515</v>
+        <v>0.7929296622768782</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5300748427479571</v>
+        <v>0.7990865711035192</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5363906864574184</v>
+        <v>0.7964985294887574</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5370353595834203</v>
+        <v>0.7852771034875923</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5385956222892773</v>
+        <v>0.7861272492921685</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5312706978924195</v>
+        <v>0.7953394475132611</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5312706978924195</v>
+        <v>0.787211122865598</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5325226477014069</v>
+        <v>0.7862768350642346</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5410901727964977</v>
+        <v>0.7751682216661695</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5462569069152672</v>
+        <v>0.7896591355770646</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5402306778811674</v>
+        <v>0.780839184491612</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5402306778811674</v>
+        <v>0.780839184491612</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5393431356335747</v>
+        <v>0.6801783477919063</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5313267925569444</v>
+        <v>0.6801783477919063</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5176486280076089</v>
+        <v>0.6476183036474829</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5267766842319145</v>
+        <v>0.6429094681976494</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5267673351211603</v>
+        <v>0.6400226705547887</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.523955122606316</v>
+        <v>0.6140865752586795</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5284865327098377</v>
+        <v>0.6268304520066516</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5253379599658612</v>
+        <v>0.6116294211944756</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5287667982744451</v>
+        <v>0.6095830047294035</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5256556219734851</v>
+        <v>0.5858055152274161</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5282623618097552</v>
+        <v>0.6053788135022766</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5200592442760589</v>
+        <v>0.6066307633112639</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5184709342379394</v>
+        <v>0.5974372633116795</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5165836604137044</v>
+        <v>0.5995954535897676</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5150607941508639</v>
+        <v>0.5999224647081457</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5203675571729286</v>
+        <v>0.6005858360556559</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5190595126994165</v>
+        <v>0.6011642343743118</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5311587163213867</v>
+        <v>0.590279999634346</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5292433951648893</v>
+        <v>0.5649603223739594</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5317753421151262</v>
+        <v>0.5589619329141053</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5435381855079642</v>
+        <v>0.5672674751500637</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5535911804228789</v>
+        <v>0.5930552312222072</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5488823449730454</v>
+        <v>0.5965025599942825</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5365215740079763</v>
+        <v>0.5965025599942825</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5424262646022722</v>
+        <v>0.5950357883959668</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5466678522724157</v>
+        <v>0.5627190288891677</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5483029078643058</v>
+        <v>0.5520957382182506</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5263096442102412</v>
+        <v>0.5381190253988331</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5110431696227863</v>
+        <v>0.5384366874064569</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5090904520232722</v>
+        <v>0.537792014280455</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5020738405232843</v>
+        <v>0.5559359374000165</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5020738405232843</v>
+        <v>0.5300559367684321</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5060445117395744</v>
+        <v>0.5035780085646164</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.504129190583077</v>
+        <v>0.5186853405112343</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5068198646581176</v>
+        <v>0.5190217007403665</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5044001070369303</v>
+        <v>0.5112669250068352</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5046897217122917</v>
+        <v>0.5085575527102865</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5021577747620547</v>
+        <v>0.5082492398134166</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5204234440794367</v>
+        <v>0.5325504872756525</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5188538322628256</v>
+        <v>0.5287285707993614</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5154062957327334</v>
+        <v>0.5287566181316239</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4999532544462293</v>
+        <v>0.523122843991181</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5002709164538531</v>
+        <v>0.5240758300140527</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4996262433278513</v>
+        <v>0.4986163316083878</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5002896146753615</v>
+        <v>0.4978407709318279</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5015509135951028</v>
+        <v>0.5021293119137588</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5002335200108367</v>
+        <v>0.5093794434245834</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4995981959955889</v>
+        <v>0.5236179313451168</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.499607545106343</v>
+        <v>0.5256921873844346</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4983181988543392</v>
+        <v>0.5223755384049005</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.5214132032712746</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5255243189068937</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5252066568992697</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5252066568992697</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5106600638398834</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5103237036107512</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5122483738780028</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5018779247134809</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.500261567343099</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4996355924386054</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4986732573049796</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4973558637207134</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4983181988543392</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4986452099727172</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5002989637861156</v>
       </c>
     </row>
   </sheetData>
